--- a/Modello_Multiplatore_a_Scalare.xlsx
+++ b/Modello_Multiplatore_a_Scalare.xlsx
@@ -8,11 +8,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tabelle" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Madre_12" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coperture" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assicurazione" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenario_Reale" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bonus_Schedine" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Madre_S0" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sequenza" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simulazione" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assicurazione" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tutte_Situazioni" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formule" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,8 +22,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0&quot;%&quot;"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.000000"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -47,16 +51,20 @@
       <sz val="11"/>
     </font>
     <font>
+      <b val="1"/>
+    </font>
+    <font>
       <color rgb="000070C0"/>
       <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="12"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00C00000"/>
-      <sz val="12"/>
+      <i val="1"/>
+      <color rgb="000070C0"/>
     </font>
     <font>
       <b val="1"/>
@@ -67,24 +75,17 @@
       <color rgb="00006100"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00C00000"/>
-    </font>
-    <font>
       <i val="1"/>
-      <color rgb="000070C0"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00006100"/>
-      <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="000070C0"/>
     </font>
+    <font>
+      <color rgb="000070C0"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -105,14 +106,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -140,49 +147,82 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1265,10 +1305,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
@@ -1284,434 +1324,441 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>1 ticket attivo. Tutti gli eventi sono PENDING all'inizio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Squadra</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Mercato</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Quota</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Esito</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Confermato</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>In Bonus?</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>In Assicurazione?</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="n">
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>TeamA - TeamB</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="D4" s="8" t="n">
+      <c r="D5" s="9" t="n">
         <v>1.32</v>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>TeamC - TeamD</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>TeamC - TeamD</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>TeamE - TeamF</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D7" s="9" t="n">
         <v>1.32</v>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>TeamG - TeamH</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>TeamE - TeamF</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>TeamI - TeamL</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="D6" s="8" t="n">
+      <c r="D9" s="9" t="n">
         <v>1.32</v>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>TeamM - TeamN</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>TeamG - TeamH</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>TeamO - TeamP</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D11" s="9" t="n">
         <v>1.32</v>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>TeamQ - TeamR</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>TeamI - TeamL</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>TeamS - TeamT</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="D8" s="8" t="n">
+      <c r="D13" s="9" t="n">
         <v>1.32</v>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E13" s="10" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G13" s="11" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>TeamU - TeamV</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>TeamM - TeamN</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>TeamW - TeamX</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="D9" s="8" t="n">
+      <c r="D15" s="9" t="n">
         <v>1.32</v>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>TeamY - TeamZ</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>TeamO - TeamP</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>UNDER 3.5</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>TeamQ - TeamR</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>UNDER 3.5</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>TeamS - TeamT</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>UNDER 3.5</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>TeamU - TeamV</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>UNDER 3.5</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>TeamW - TeamX</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>UNDER 3.5</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>TeamY - TeamZ</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>UNDER 3.5</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G16" s="11" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -1747,10 +1794,10 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Raw multipla (1.32^N)</t>
-        </is>
-      </c>
-      <c r="B23" s="9">
+          <t>Raw multipla = 1.32^N</t>
+        </is>
+      </c>
+      <c r="B23" s="12">
         <f>B22^B21</f>
         <v/>
       </c>
@@ -1758,10 +1805,10 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>N per BONUS</t>
-        </is>
-      </c>
-      <c r="B24">
+          <t>N per BONUS (tutte pending)</t>
+        </is>
+      </c>
+      <c r="B24" s="5">
         <f>MIN(B21,12)</f>
         <v/>
       </c>
@@ -1769,10 +1816,10 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>% BONUS (tabella)</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
+          <t>% BONUS (da tabella)</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="n">
         <v>59.4</v>
       </c>
     </row>
@@ -1782,7 +1829,7 @@
           <t>Moltiplicatore FINALE</t>
         </is>
       </c>
-      <c r="B26" s="10">
+      <c r="B26" s="14">
         <f>B23*(1+B25/100)</f>
         <v/>
       </c>
@@ -1793,7 +1840,7 @@
           <t>Stake (round 50c)</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="B27" s="9" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1803,7 +1850,7 @@
           <t>Vincita Lorda</t>
         </is>
       </c>
-      <c r="B28" s="11">
+      <c r="B28" s="15">
         <f>B27*B26</f>
         <v/>
       </c>
@@ -1824,8 +1871,19 @@
           <t>Costo Totale ciclo</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="B30" s="9" t="n">
         <v>221</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>EV con assicurazione</t>
+        </is>
+      </c>
+      <c r="B31" s="15">
+        <f>(0.025*B28)-(0.51*B30)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1839,7 +1897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1857,375 +1915,628 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>COPERTURE SEQUENCIALI - BONUS DECRESCENTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+          <t>TIMELINE SEQUENZIALE - UN SOLO TICKET ATTIVO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Regola: solo 1 ticket attivo alla volta. Dopo ogni esito, si piazza il successivo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Step</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Eventi Totali</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>N_pending</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>N_bonus</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Eventi Totali (N_int)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>N_pending (N_slip)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>% BONUS</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Quote</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Quote Raw</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Molt.Finale</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Stake</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>Vincita</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>Cum.Cost</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Cop.1</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Cumulative Spesa</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Esito</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>S0</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Madre</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="F5" s="6">
+        <f>3*1.32^D5</f>
+        <v/>
+      </c>
+      <c r="G5" s="16">
+        <f>F5*(1+E5/100)</f>
+        <v/>
+      </c>
+      <c r="H5" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Copertura</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="D6" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="E6" s="13" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="F6" s="6">
+        <f>3*1.32^11</f>
+        <v/>
+      </c>
+      <c r="G6" s="6">
+        <f>F6*(1+E6/100)</f>
+        <v/>
+      </c>
+      <c r="H6" s="9">
+        <f>ROUND((I5+45)/(G6-1),0)</f>
+        <v/>
+      </c>
+      <c r="I6" s="9">
+        <f>I5+H6</f>
+        <v/>
+      </c>
+      <c r="J6" s="18" t="inlineStr">
+        <is>
+          <t>CONDIZIONALE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Copertura</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="E4" s="12" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="F4" s="13">
-        <f>1.32^C4</f>
-        <v/>
-      </c>
-      <c r="G4" s="13">
-        <f>F4*(1+E4/100)</f>
-        <v/>
-      </c>
-      <c r="H4" s="5" t="n">
+      <c r="D7" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="F7" s="6">
+        <f>3*1.32^10</f>
+        <v/>
+      </c>
+      <c r="G7" s="6">
+        <f>F7*(1+E7/100)</f>
+        <v/>
+      </c>
+      <c r="H7" s="9">
+        <f>ROUND((I6+45)/(G7-1),0)</f>
+        <v/>
+      </c>
+      <c r="I7" s="9">
+        <f>I6+H7</f>
+        <v/>
+      </c>
+      <c r="J7" s="18" t="inlineStr">
+        <is>
+          <t>CONDIZIONALE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Copertura</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="F8" s="6">
+        <f>3*1.32^9</f>
+        <v/>
+      </c>
+      <c r="G8" s="6">
+        <f>F8*(1+E8/100)</f>
+        <v/>
+      </c>
+      <c r="H8" s="9">
+        <f>ROUND((I7+45)/(G8-1),0)</f>
+        <v/>
+      </c>
+      <c r="I8" s="9">
+        <f>I7+H8</f>
+        <v/>
+      </c>
+      <c r="J8" s="18" t="inlineStr">
+        <is>
+          <t>CONDIZIONALE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Copertura</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="F9" s="6">
+        <f>3*1.32^8</f>
+        <v/>
+      </c>
+      <c r="G9" s="6">
+        <f>F9*(1+E9/100)</f>
+        <v/>
+      </c>
+      <c r="H9" s="9">
+        <f>ROUND((I8+45)/(G9-1),0)</f>
+        <v/>
+      </c>
+      <c r="I9" s="9">
+        <f>I8+H9</f>
+        <v/>
+      </c>
+      <c r="J9" s="18" t="inlineStr">
+        <is>
+          <t>CONDIZIONALE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Copertura</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="F10" s="6">
+        <f>3*1.32^7</f>
+        <v/>
+      </c>
+      <c r="G10" s="6">
+        <f>F10*(1+E10/100)</f>
+        <v/>
+      </c>
+      <c r="H10" s="9">
+        <f>ROUND((I9+45)/(G10-1),0)</f>
+        <v/>
+      </c>
+      <c r="I10" s="9">
+        <f>I9+H10</f>
+        <v/>
+      </c>
+      <c r="J10" s="18" t="inlineStr">
+        <is>
+          <t>CONDIZIONALE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Copertura</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F11" s="6">
+        <f>3*1.32^6</f>
+        <v/>
+      </c>
+      <c r="G11" s="6">
+        <f>F11*(1+E11/100)</f>
+        <v/>
+      </c>
+      <c r="H11" s="9">
+        <f>ROUND((I10+45)/(G11-1),0)</f>
+        <v/>
+      </c>
+      <c r="I11" s="9">
+        <f>I10+H11</f>
+        <v/>
+      </c>
+      <c r="J11" s="18" t="inlineStr">
+        <is>
+          <t>CONDIZIONALE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Copertura</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" s="6">
+        <f>3*1.32^5</f>
+        <v/>
+      </c>
+      <c r="G12" s="6">
+        <f>F12*(1+E12/100)</f>
+        <v/>
+      </c>
+      <c r="H12" s="9">
+        <f>ROUND((I11+45)/(G12-1),0)</f>
+        <v/>
+      </c>
+      <c r="I12" s="9">
+        <f>I11+H12</f>
+        <v/>
+      </c>
+      <c r="J12" s="18" t="inlineStr">
+        <is>
+          <t>CONDIZIONALE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>C8</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Copertura</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="5" t="n">
+      <c r="F13" s="6">
+        <f>3*1.32^4</f>
+        <v/>
+      </c>
+      <c r="G13" s="6">
+        <f>F13*(1+E13/100)</f>
+        <v/>
+      </c>
+      <c r="H13" s="9">
+        <f>ROUND((I12+45)/(G13-1),0)</f>
+        <v/>
+      </c>
+      <c r="I13" s="9">
+        <f>I12+H13</f>
+        <v/>
+      </c>
+      <c r="J13" s="18" t="inlineStr">
+        <is>
+          <t>CONDIZIONALE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Copertura</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="5" t="n">
+      <c r="F14" s="6">
+        <f>3*1.32^3</f>
+        <v/>
+      </c>
+      <c r="G14" s="6">
+        <f>F14*(1+E14/100)</f>
+        <v/>
+      </c>
+      <c r="H14" s="9">
+        <f>ROUND((I13+45)/(G14-1),0)</f>
+        <v/>
+      </c>
+      <c r="I14" s="9">
+        <f>I13+H14</f>
+        <v/>
+      </c>
+      <c r="J14" s="18" t="inlineStr">
+        <is>
+          <t>CONDIZIONALE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Copertura</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="13" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Cop.2</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="E5" s="12" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="F5" s="13">
-        <f>1.32^C5</f>
-        <v/>
-      </c>
-      <c r="G5" s="13">
-        <f>F5*(1+E5/100)</f>
-        <v/>
-      </c>
-      <c r="H5" s="5" t="n">
+      <c r="F15" s="6">
+        <f>3*1.32^2</f>
+        <v/>
+      </c>
+      <c r="G15" s="6">
+        <f>F15*(1+E15/100)</f>
+        <v/>
+      </c>
+      <c r="H15" s="9">
+        <f>ROUND((I14+45)/(G15-1),0)</f>
+        <v/>
+      </c>
+      <c r="I15" s="9">
+        <f>I14+H15</f>
+        <v/>
+      </c>
+      <c r="J15" s="18" t="inlineStr">
+        <is>
+          <t>CONDIZIONALE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>EX</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Exchange</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="5" t="n">
+      <c r="E16" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Cop.3</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="E6" s="12" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="F6" s="13">
-        <f>1.32^C6</f>
-        <v/>
-      </c>
-      <c r="G6" s="13">
-        <f>F6*(1+E6/100)</f>
-        <v/>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Cop.4</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="E7" s="12" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="F7" s="13">
-        <f>1.32^C7</f>
-        <v/>
-      </c>
-      <c r="G7" s="13">
-        <f>F7*(1+E7/100)</f>
-        <v/>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Cop.5</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E8" s="12" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="F8" s="13">
-        <f>1.32^C8</f>
-        <v/>
-      </c>
-      <c r="G8" s="13">
-        <f>F8*(1+E8/100)</f>
-        <v/>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Cop.6</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E9" s="12" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="F9" s="13">
-        <f>1.32^C9</f>
-        <v/>
-      </c>
-      <c r="G9" s="13">
-        <f>F9*(1+E9/100)</f>
-        <v/>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Cop.7</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E10" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="13">
-        <f>1.32^C10</f>
-        <v/>
-      </c>
-      <c r="G10" s="13">
-        <f>F10*(1+E10/100)</f>
-        <v/>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>STEP 7: NESSUN BONUS -&gt; ASSICURAZIONE ATTIVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="F16" s="19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="G16" s="16">
+        <f>F16</f>
+        <v/>
+      </c>
+      <c r="H16" s="9">
+        <f>ROUND((I15+45)/(G16-1),0)</f>
+        <v/>
+      </c>
+      <c r="I16" s="9">
+        <f>I15+H16</f>
+        <v/>
+      </c>
+      <c r="J16" s="11" t="inlineStr">
+        <is>
+          <t>LOCK</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>RIEPILOGO</t>
         </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Costo Madre S0</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Costo Coperture</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Costo Totale</t>
-        </is>
-      </c>
-      <c r="B18" s="15">
-        <f>B16+SUM(H8:H10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Vincita se Madre vince</t>
-        </is>
-      </c>
-      <c r="B19">
-        <f>B18*1.32^12*1.594</f>
-        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Costo Madre S0</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Costo Totale Ciclo (fino a lock)</t>
+        </is>
+      </c>
+      <c r="B21" s="20">
+        <f>SUM(H5:H16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Vincita se S0 vince</t>
+        </is>
+      </c>
+      <c r="B22" s="15">
+        <f>G5*H5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Vincita se C7 vince</t>
         </is>
       </c>
-      <c r="B20">
-        <f>H10*G10</f>
+      <c r="B23" s="9">
+        <f>G12*H12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Vincita Lock Exchange</t>
+        </is>
+      </c>
+      <c r="B24" s="15">
+        <f>G16*H16</f>
         <v/>
       </c>
     </row>
@@ -2240,357 +2551,717 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CALCOLO ASSICURAZIONE - STEP 5 EVENTI</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="16" t="inlineStr">
-        <is>
-          <t>Regola: N_internal=confermati+pending | N_slip=sole pending</t>
+          <t>SIMULAZIONE - Over al 4° evento</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>M1-M3 UNDER, M4 OVER. Dopo M4, S0 muore e C4 diventa ticket attivo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Partita</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Esito</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Ticket Attivo</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>N_total</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>N_pending</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>% Bonus</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Quote Raw</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Molt.Finale</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Stake</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Cumulative</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Esito Ticket</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
-        <is>
-          <t>Scenario: M1-M7 UNDER, M8 OVER (Madre persa)</t>
+      <c r="A5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>S0</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G5" s="13" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="H5" s="6">
+        <f>3*1.32^F5</f>
+        <v/>
+      </c>
+      <c r="I5" s="6">
+        <f>H5*(1+G5/100)</f>
+        <v/>
+      </c>
+      <c r="J5" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>ATTIVO</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>S0</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G6" s="13" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="H6" s="6">
+        <f>3*1.32^F6</f>
+        <v/>
+      </c>
+      <c r="I6" s="6">
+        <f>H6*(1+G6/100)</f>
+        <v/>
+      </c>
+      <c r="K6" s="9">
+        <f>K5</f>
+        <v/>
+      </c>
+      <c r="L6" s="11" t="inlineStr">
+        <is>
+          <t>ATTIVO</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Evento</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Squadra</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Stato</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>In Conteggio?</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>In Bonus?</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>In Assicurazione?</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>Note</t>
+      <c r="A7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>S0</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="H7" s="6">
+        <f>3*1.32^F7</f>
+        <v/>
+      </c>
+      <c r="I7" s="6">
+        <f>H7*(1+G7/100)</f>
+        <v/>
+      </c>
+      <c r="K7" s="9">
+        <f>K6</f>
+        <v/>
+      </c>
+      <c r="L7" s="11" t="inlineStr">
+        <is>
+          <t>ATTIVO</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>S0-&gt;C4</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G8" s="13" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="H8" s="6">
+        <f>3*1.32^F8</f>
+        <v/>
+      </c>
+      <c r="I8" s="6">
+        <f>H8*(1+G8/100)</f>
+        <v/>
+      </c>
+      <c r="K8" s="9">
+        <f>K7</f>
+        <v/>
+      </c>
+      <c r="L8" s="21" t="inlineStr">
+        <is>
+          <t>MORTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="H9" s="6">
+        <f>3*1.32^F9</f>
+        <v/>
+      </c>
+      <c r="I9" s="6">
+        <f>H9*(1+G9/100)</f>
+        <v/>
+      </c>
+      <c r="J9" s="17">
+        <f>ROUND((K8+45)/I9,0)</f>
+        <v/>
+      </c>
+      <c r="K9" s="17">
+        <f>K8+J9</f>
+        <v/>
+      </c>
+      <c r="L9" s="18" t="inlineStr">
+        <is>
+          <t>NUOVO</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G10" s="13" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="H10" s="6">
+        <f>3*1.32^F10</f>
+        <v/>
+      </c>
+      <c r="I10" s="6">
+        <f>H10*(1+G10/100)</f>
+        <v/>
+      </c>
+      <c r="K10" s="9">
+        <f>K9</f>
+        <v/>
+      </c>
+      <c r="L10" s="18" t="inlineStr">
+        <is>
+          <t>NUOVO</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G11" s="13" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="H11" s="6">
+        <f>3*1.32^F11</f>
+        <v/>
+      </c>
+      <c r="I11" s="6">
+        <f>H11*(1+G11/100)</f>
+        <v/>
+      </c>
+      <c r="K11" s="9">
+        <f>K10</f>
+        <v/>
+      </c>
+      <c r="L11" s="18" t="inlineStr">
+        <is>
+          <t>NUOVO</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>M8</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>TeamQ-TeamR</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="G8" s="18" t="inlineStr">
-        <is>
-          <t>Già risolta</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G12" s="13" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="H12" s="6">
+        <f>3*1.32^F12</f>
+        <v/>
+      </c>
+      <c r="I12" s="6">
+        <f>H12*(1+G12/100)</f>
+        <v/>
+      </c>
+      <c r="K12" s="9">
+        <f>K11</f>
+        <v/>
+      </c>
+      <c r="L12" s="18" t="inlineStr">
+        <is>
+          <t>NUOVO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>M9</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>TeamS-TeamT</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G13" s="13" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="H13" s="6">
+        <f>3*1.32^F13</f>
+        <v/>
+      </c>
+      <c r="I13" s="6">
+        <f>H13*(1+G13/100)</f>
+        <v/>
+      </c>
+      <c r="K13" s="9">
+        <f>K12</f>
+        <v/>
+      </c>
+      <c r="L13" s="18" t="inlineStr">
+        <is>
+          <t>NUOVO</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F9" s="18" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="G9" s="18" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="18" t="inlineStr">
-        <is>
-          <t>M10</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>TeamU-TeamV</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G14" s="13" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="H14" s="6">
+        <f>3*1.32^F14</f>
+        <v/>
+      </c>
+      <c r="I14" s="6">
+        <f>H14*(1+G14/100)</f>
+        <v/>
+      </c>
+      <c r="K14" s="9">
+        <f>K13</f>
+        <v/>
+      </c>
+      <c r="L14" s="18" t="inlineStr">
+        <is>
+          <t>NUOVO</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G15" s="13" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="H15" s="6">
+        <f>3*1.32^F15</f>
+        <v/>
+      </c>
+      <c r="I15" s="6">
+        <f>H15*(1+G15/100)</f>
+        <v/>
+      </c>
+      <c r="K15" s="9">
+        <f>K14</f>
+        <v/>
+      </c>
+      <c r="L15" s="18" t="inlineStr">
+        <is>
+          <t>NUOVO</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F10" s="18" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="G10" s="18" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="18" t="inlineStr">
-        <is>
-          <t>M11</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>TeamW-TeamX</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F11" s="18" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="G11" s="18" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="18" t="inlineStr">
-        <is>
-          <t>M12</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>TeamY-TeamZ</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F12" s="18" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="G12" s="18" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>CALCOLO</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>N_internal (conf+pending)</t>
-        </is>
-      </c>
-      <c r="B16">
-        <f>1+4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>N_slip (solo pending)</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Quote (1.32^N_slip)</t>
-        </is>
-      </c>
-      <c r="B18" s="9">
-        <f>1.32^B17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>% BONUS (N_slip=4)</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="H16" s="6">
+        <f>3*1.32^F16</f>
+        <v/>
+      </c>
+      <c r="I16" s="6">
+        <f>H16*(1+G16/100)</f>
+        <v/>
+      </c>
+      <c r="K16" s="9">
+        <f>K15</f>
+        <v/>
+      </c>
+      <c r="L16" s="18" t="inlineStr">
+        <is>
+          <t>NUOVO</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Moltiplicatore FINALE</t>
-        </is>
-      </c>
-      <c r="B20" s="19">
-        <f>B18*(1+B19/100)</f>
-        <v/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>RISULTATO SIMULAZIONE</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Stake Step</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>25</v>
+          <t>S0 morta - stake perso</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Vincita Lorda</t>
-        </is>
-      </c>
-      <c r="B22">
-        <f>B22*B20</f>
+          <t>C4 stake piazzata</t>
+        </is>
+      </c>
+      <c r="B22" s="9">
+        <f>J9</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ASSICURAZIONE 1 errore (60%)</t>
+          <t>Totale speso</t>
         </is>
       </c>
       <c r="B23" s="20">
-        <f>MIN(B22,50)*0.60</f>
+        <f>K16</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ASSICURAZIONE 2 errori (30%)</t>
-        </is>
-      </c>
-      <c r="B24">
-        <f>MIN(B22,50)*0.30</f>
+          <t>Se M5-M12 tutte Under -&gt; C4 vince</t>
+        </is>
+      </c>
+      <c r="B24" s="15">
+        <f>I9*J9-K16</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ASSICURAZIONE 3 errori (10%)</t>
-        </is>
-      </c>
-      <c r="B25">
-        <f>MIN(B22,50)*0.10</f>
-        <v/>
+          <t>Se M5-M12 un'altra Over -&gt; C4 muore, C5 attiva</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Vedi tabella Assicurazione</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2604,268 +3275,259 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SCENARIO REALE - 7 UNDER + 1 OVER + 4 PENDING</t>
+          <t>ASSICURAZIONE - CALCOLO SEPARATO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Regola: N_internal = confermate + pending. Non entra nel prodotto quote né nel bonus.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Step</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Eventi Tot</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>N_pending</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Bonus%</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Quote</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Molt.Fin</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Stake</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>Vincita</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>Esito</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>TABELLA ASSICURAZIONE (N_internal &gt;= 4)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>S0</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Madre</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="E5" s="12" t="n">
-        <v>59.4</v>
-      </c>
-      <c r="F5" s="8">
-        <f>1.32^12</f>
-        <v/>
-      </c>
-      <c r="G5" s="13">
-        <f>F5*(1+E5/100)</f>
-        <v/>
-      </c>
-      <c r="H5" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" s="8">
-        <f>H5*G5</f>
-        <v/>
-      </c>
-      <c r="J5" s="21" t="inlineStr">
-        <is>
-          <t>PERSA</t>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>N Eventi</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>1 Errore</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>2 Errori</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>3 Errori</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Rimborso Max</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>C8</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Copertura</t>
-        </is>
+      <c r="A6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>30</v>
       </c>
       <c r="C6" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E6" s="12" t="n"/>
-      <c r="F6" s="8">
-        <f>1.32^4</f>
-        <v/>
-      </c>
-      <c r="G6" s="13">
-        <f>F6*(1+E6/100)</f>
-        <v/>
-      </c>
-      <c r="H6" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="I6" s="8">
-        <f>H6*G6</f>
-        <v/>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>ATTIVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>C8-EX</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Exchange</t>
-        </is>
+      <c r="B7" s="5" t="n">
+        <v>60</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="12" t="n"/>
-      <c r="F7" s="8" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="G7" s="13">
-        <f>F7</f>
-        <v/>
-      </c>
-      <c r="H7" s="8" t="n">
-        <v>120</v>
-      </c>
-      <c r="I7" s="8">
-        <f>H7*G7</f>
-        <v/>
-      </c>
-      <c r="J7" s="18" t="inlineStr">
-        <is>
-          <t>LOCK</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>RIEPILOGO EV</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Spesa Totale Ciclo</t>
-        </is>
-      </c>
-      <c r="B12">
-        <f>H5+H6+H7</f>
-        <v/>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>ESAME ASSICURAZIONE - C4 (N_int=8)</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Vincita Madre (0 errori)</t>
-        </is>
-      </c>
-      <c r="B13">
-        <f>G5*H5</f>
-        <v/>
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>Dopo M4 Over, C4 ha 7 pending + 1 confermato = N_int=8</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>P(0 errori)</t>
-        </is>
-      </c>
-      <c r="B14" s="9">
-        <f>0.7576^12</f>
-        <v/>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Parametro</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Valore</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Formula/Note</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P(1 errore)</t>
-        </is>
-      </c>
-      <c r="B15" s="9">
-        <f>12*0.3333*0.7576^11</f>
-        <v/>
+          <t>N_internal (confermate+pending)</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>1 confermata(M4 Over) + 7 pending</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P(2+ errori)</t>
-        </is>
-      </c>
-      <c r="B16" s="9">
-        <f>1-B14-B15</f>
-        <v/>
+          <t>N_slip (solo pending)</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Solo per bonus: tabella_bonus[7]=19.1%</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EV Totale</t>
-        </is>
-      </c>
-      <c r="B17" s="22">
-        <f>(B14*B13)-(B16*B12*0.4)</f>
+          <t>N per tabella assicurazione</t>
+        </is>
+      </c>
+      <c r="B17" s="5">
+        <f>MIN(B15,7)</f>
+        <v/>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>MIN(N_int, 7+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Stake C4</t>
+        </is>
+      </c>
+      <c r="B18" s="9">
+        <f>Simulazione!J9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Rimborso 1 errore (100%)</t>
+        </is>
+      </c>
+      <c r="B19" s="24">
+        <f>MIN(B18,50)*1.00</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Rimborso 2 errori (80%)</t>
+        </is>
+      </c>
+      <c r="B20" s="9">
+        <f>MIN(B18,50)*0.80</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Rimborso 3 errori (60%)</t>
+        </is>
+      </c>
+      <c r="B21" s="9">
+        <f>MIN(B18,50)*0.60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Rimborso 4+ errori (0%)</t>
+        </is>
+      </c>
+      <c r="B22" s="9">
+        <f>0</f>
         <v/>
       </c>
     </row>
@@ -2880,378 +3542,972 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SCHEMA SCHEDINE - FORMULA COMPLETA</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>FORMULE GENERALI</t>
+          <t>TUTTE LE SITUAZIONI POSSIBILI - 12 EVENTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Tabella completa degli scenari. Solo 1 ticket attivo alla volta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Errori</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Posizione Errori</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Stato Finale</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Spesa Totale</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Vincita</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Netto</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>ROI</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Note</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="inlineStr">
-        <is>
-          <t>N_eventi_totali</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Conteggio eventi (confermati+pending)</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>E0</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Nessun</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>Vittoria S0</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr"/>
+      <c r="F5" s="9" t="inlineStr"/>
+      <c r="G5" s="9" t="inlineStr"/>
+      <c r="H5" s="25" t="inlineStr"/>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Madre vince, nessun errore</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="23" t="inlineStr">
-        <is>
-          <t>N_slip</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>Sole eventi PENDING (per quote e bonus)</t>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>E1(k=1)</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>C1 attiva</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr"/>
+      <c r="F6" s="9" t="inlineStr"/>
+      <c r="G6" s="9" t="inlineStr"/>
+      <c r="H6" s="25" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Un solo Over alla 1</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="inlineStr">
-        <is>
-          <t>N_bonus</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>MIN(N_slip,max_bonus) - per tabella bonus</t>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>E1(k=2)</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>C2 attiva</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr"/>
+      <c r="F7" s="9" t="inlineStr"/>
+      <c r="G7" s="9" t="inlineStr"/>
+      <c r="H7" s="25" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>Un solo Over alla 2</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="23" t="inlineStr">
-        <is>
-          <t>raw_odds</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>underOdds^N_slip</t>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>E1(k=3)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>C3 attiva</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr"/>
+      <c r="F8" s="9" t="inlineStr"/>
+      <c r="G8" s="9" t="inlineStr"/>
+      <c r="H8" s="25" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>Un solo Over alla 3</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="23" t="inlineStr">
-        <is>
-          <t>bonus_pct</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>Tabelle[N_bonus]</t>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>E1(k=4)</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>C4 attiva</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr"/>
+      <c r="F9" s="9" t="inlineStr"/>
+      <c r="G9" s="9" t="inlineStr"/>
+      <c r="H9" s="25" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Un solo Over alla 4</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="23" t="inlineStr">
-        <is>
-          <t>final_odds</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>raw_odds*(1+bonus_pct/100)</t>
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>E1(k=5)</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>C5 attiva</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr"/>
+      <c r="F10" s="9" t="inlineStr"/>
+      <c r="G10" s="9" t="inlineStr"/>
+      <c r="H10" s="25" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Un solo Over alla 5</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="23" t="inlineStr">
-        <is>
-          <t>stake</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>ROUND50[(speso+finance)/(final_odds-1)]</t>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>E1(k=6)</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>C6 attiva</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr"/>
+      <c r="F11" s="9" t="inlineStr"/>
+      <c r="G11" s="9" t="inlineStr"/>
+      <c r="H11" s="25" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Un solo Over alla 6</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="23" t="inlineStr">
-        <is>
-          <t>gross_win</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>stake*final_odds</t>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>E1(k=7)</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>C7 attiva</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr"/>
+      <c r="F12" s="9" t="inlineStr"/>
+      <c r="G12" s="9" t="inlineStr"/>
+      <c r="H12" s="25" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Un solo Over alla 7</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="23" t="inlineStr">
-        <is>
-          <t>net_profit</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>gross_win-cumulative_cost</t>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>E1(k=8)</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>M8</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>C8 attiva</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr"/>
+      <c r="F13" s="9" t="inlineStr"/>
+      <c r="G13" s="9" t="inlineStr"/>
+      <c r="H13" s="25" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Un solo Over alla 8</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="23" t="inlineStr">
-        <is>
-          <t>ROI</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>(net_profit/cumulative_cost)*100</t>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>E1(k=9)</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>M9</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>C9 attiva</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr"/>
+      <c r="F14" s="9" t="inlineStr"/>
+      <c r="G14" s="9" t="inlineStr"/>
+      <c r="H14" s="25" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Un solo Over alla 9</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="23" t="inlineStr">
-        <is>
-          <t>insurance_refund</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>MIN(stake,50)*tabella_assicurazione[N,errori]</t>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>E1(k=10)</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>C10 attiva</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr"/>
+      <c r="F15" s="9" t="inlineStr"/>
+      <c r="G15" s="9" t="inlineStr"/>
+      <c r="H15" s="25" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Un solo Over alla 10</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="23" t="inlineStr">
-        <is>
-          <t>internal_count</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>confermati+pending - SOLO per assicurazione</t>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>E1(k=11)</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>C11 attiva</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr"/>
+      <c r="F16" s="9" t="inlineStr"/>
+      <c r="G16" s="9" t="inlineStr"/>
+      <c r="H16" s="25" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Un solo Over alla 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>E1(k=12)</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Lock Exchange</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr"/>
+      <c r="F17" s="9" t="inlineStr"/>
+      <c r="G17" s="9" t="inlineStr"/>
+      <c r="H17" s="25" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Un solo Over all'ultimo</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>E2(1,2)</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>M1,M2</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C2 attiva</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr"/>
+      <c r="F18" s="9" t="inlineStr"/>
+      <c r="G18" s="9" t="inlineStr"/>
+      <c r="H18" s="25" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Due errori consecutivi</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>ESEMPIO: Madre 12 eventi, stake=2EUR</t>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>E2(1,5)</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>M1,M5</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>C5 attiva</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr"/>
+      <c r="F19" s="9" t="inlineStr"/>
+      <c r="G19" s="9" t="inlineStr"/>
+      <c r="H19" s="25" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Due errori sparsi</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Parametro</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Valore</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Formula</t>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>E2(4,8)</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>M4,M8</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>C8 attiva</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr"/>
+      <c r="F20" s="9" t="inlineStr"/>
+      <c r="G20" s="9" t="inlineStr"/>
+      <c r="H20" s="25" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Due errori sparsi</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>N_eventi_totali</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>Conteggio</t>
+          <t>E3(1,2,3)</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>M1,M2,M3</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>C3 attiva</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr"/>
+      <c r="F21" s="9" t="inlineStr"/>
+      <c r="G21" s="9" t="inlineStr"/>
+      <c r="H21" s="25" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Tre errori consecutivi</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>N_slip</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>Solo pending</t>
+          <t>E3(1,4,8)</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>M1,M4,M8</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>C8 attiva</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr"/>
+      <c r="F22" s="9" t="inlineStr"/>
+      <c r="G22" s="9" t="inlineStr"/>
+      <c r="H22" s="25" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Tre errori sparsi</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>N_bonus</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>MIN(12,12)</t>
+          <t>E4(1,2,3,4)</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>M1-M4</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>C4 attiva</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr"/>
+      <c r="F23" s="9" t="inlineStr"/>
+      <c r="G23" s="9" t="inlineStr"/>
+      <c r="H23" s="25" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Quattro errori - raro</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>underOdds</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>Input</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+          <t>E12</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Tutti</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>Lock Exchange</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr"/>
+      <c r="F24" s="9" t="inlineStr"/>
+      <c r="G24" s="9" t="inlineStr"/>
+      <c r="H24" s="25" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Tutti Over - singola exchange</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>SINTESI</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Scenario piu probabile</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>E1 - 1 errore (P=27.4%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Scenario migliore</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>E0 - Madre vince (P=8.2%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Scenario peggiore</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>E12 - Tutti Over (P&lt;0.1%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Con assicurazione:</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>P(2+ errori) coperto da rimborso</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SCHEMA FORMULE COMPLETO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Parametro</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="26" t="inlineStr">
+        <is>
+          <t>N_eventi_totali</t>
+        </is>
+      </c>
+      <c r="B4" s="27" t="inlineStr">
+        <is>
+          <t>Conteggio eventi nella schedina</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>confermate + pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="26" t="inlineStr">
+        <is>
+          <t>N_slip</t>
+        </is>
+      </c>
+      <c r="B5" s="27" t="inlineStr">
+        <is>
+          <t>Sole eventi PENDING</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>per calcolo quote e bonus</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="26" t="inlineStr">
+        <is>
+          <t>N_bonus</t>
+        </is>
+      </c>
+      <c r="B6" s="27" t="inlineStr">
+        <is>
+          <t>MIN(N_slip, max_bonus_events)</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>per lookup tabella bonus</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="26" t="inlineStr">
         <is>
           <t>raw_odds</t>
         </is>
       </c>
-      <c r="B25" s="8">
-        <f>1.32^C23</f>
-        <v/>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>Formula</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="B7" s="27" t="inlineStr">
+        <is>
+          <t>underOdds^N_slip</t>
+        </is>
+      </c>
+      <c r="C7" s="28" t="inlineStr">
+        <is>
+          <t>prodotto sole pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="26" t="inlineStr">
         <is>
           <t>bonus_pct</t>
         </is>
       </c>
-      <c r="B26" s="8" t="n">
-        <v>59.4</v>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>Tabelle</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="B8" s="27" t="inlineStr">
+        <is>
+          <t>Tabelle[N_bonus]</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="inlineStr">
+        <is>
+          <t>lookup da tabella</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="26" t="inlineStr">
         <is>
           <t>final_odds</t>
         </is>
       </c>
-      <c r="B27" s="8">
-        <f>D24*(1+F23/100)</f>
-        <v/>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>Formula</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>speso_fino_ad_ora</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>Base stake</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>target_profit</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="n">
-        <v>45</v>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>Input</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
+        <is>
+          <t>raw_odds * (1 + bonus_pct/100)</t>
+        </is>
+      </c>
+      <c r="C9" s="28" t="inlineStr">
+        <is>
+          <t>multiplatore finale</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="26" t="inlineStr">
         <is>
           <t>stake</t>
         </is>
       </c>
-      <c r="B30" s="8">
-        <f>ROUND((H24+I24)/(G24-1),0)</f>
-        <v/>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>Formula</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="B10" s="27" t="inlineStr">
+        <is>
+          <t>ROUND50[(speso_fino_ora + target) / (final_odds - 1)]</t>
+        </is>
+      </c>
+      <c r="C10" s="28" t="inlineStr">
+        <is>
+          <t>solo se ticket piazzato</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>cumulative</t>
+        </is>
+      </c>
+      <c r="B11" s="27" t="inlineStr">
+        <is>
+          <t>speso_precedente + stake_corrente</t>
+        </is>
+      </c>
+      <c r="C11" s="28" t="inlineStr">
+        <is>
+          <t>costo effettivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="26" t="inlineStr">
         <is>
           <t>gross_win</t>
         </is>
       </c>
-      <c r="B31" s="8">
-        <f>J24*G24</f>
-        <v/>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>Formula</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="B12" s="27" t="inlineStr">
+        <is>
+          <t>stake * final_odds</t>
+        </is>
+      </c>
+      <c r="C12" s="28" t="inlineStr">
+        <is>
+          <t>vincita lorda ticket</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>net_profit</t>
+        </is>
+      </c>
+      <c r="B13" s="27" t="inlineStr">
+        <is>
+          <t>gross_win - cumulative</t>
+        </is>
+      </c>
+      <c r="C13" s="28" t="inlineStr">
+        <is>
+          <t>profitto netto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="26" t="inlineStr">
         <is>
           <t>ROI</t>
         </is>
       </c>
-      <c r="B32" s="8">
-        <f>(K24-J24)/J24*100</f>
-        <v/>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>Formula</t>
+      <c r="B14" s="27" t="inlineStr">
+        <is>
+          <t>(net_profit / cumulative) * 100</t>
+        </is>
+      </c>
+      <c r="C14" s="28" t="inlineStr">
+        <is>
+          <t>rendimento percentuale</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>insurance_refund</t>
+        </is>
+      </c>
+      <c r="B15" s="27" t="inlineStr">
+        <is>
+          <t>MIN(stake, 50) * tabella_assicurazione[N_int, errori]</t>
+        </is>
+      </c>
+      <c r="C15" s="28" t="inlineStr">
+        <is>
+          <t>solo se assicurabile</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>internal_count</t>
+        </is>
+      </c>
+      <c r="B16" s="27" t="inlineStr">
+        <is>
+          <t>confermate + pending</t>
+        </is>
+      </c>
+      <c r="C16" s="28" t="inlineStr">
+        <is>
+          <t>SOLO per assicurazione</t>
         </is>
       </c>
     </row>

--- a/Modello_Multiplatore_a_Scalare.xlsx
+++ b/Modello_Multiplatore_a_Scalare.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assicurazione" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tutte_Situazioni" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formule" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simulazione_M2" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4282,4 +4283,574 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SIMULAZIONE - Madre muore alla 2a partita (15 eventi)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>M1 Under (Madre attiva), M2 OVER (Madre muore, 2EUR persi), C2 diventa madre: la sua vincita copre speso precedente + target</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Evento</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Esito</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Attivo</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>N_pending</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Finale</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Stake</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Spesa_cum</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Lordo</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>Netto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>S0/M1</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Madre</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="F5" s="9">
+        <f>1.32^15</f>
+        <v/>
+      </c>
+      <c r="G5" s="9">
+        <f>F5*(1+89.8/100)</f>
+        <v/>
+      </c>
+      <c r="H5" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" s="8">
+        <f>H5*G5</f>
+        <v/>
+      </c>
+      <c r="K5" s="8">
+        <f>J5-I5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>S0-&gt;C2</t>
+        </is>
+      </c>
+      <c r="E6" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="F6" s="25">
+        <f>1.32^13</f>
+        <v/>
+      </c>
+      <c r="G6" s="25">
+        <f>F6*(1+68.9/100)</f>
+        <v/>
+      </c>
+      <c r="H6" s="23">
+        <f>ROUNDUP((I5+45)/(G6-1)/0.5,0)*0.5</f>
+        <v/>
+      </c>
+      <c r="I6" s="23">
+        <f>I5+H6</f>
+        <v/>
+      </c>
+      <c r="J6" s="23">
+        <f>H6*G6</f>
+        <v/>
+      </c>
+      <c r="K6" s="23">
+        <f>J6-I6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>C2/M3</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>C2 (=madre)</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" s="11">
+        <f>1.32^12</f>
+        <v/>
+      </c>
+      <c r="G7" s="11">
+        <f>F7*(1+59.4/100)</f>
+        <v/>
+      </c>
+      <c r="H7" s="6">
+        <f>ROUNDUP((I6+45)/(G7-1)/0.5,0)*0.5</f>
+        <v/>
+      </c>
+      <c r="I7" s="6">
+        <f>I6+H7</f>
+        <v/>
+      </c>
+      <c r="J7" s="6">
+        <f>H7*G7</f>
+        <v/>
+      </c>
+      <c r="K7" s="6">
+        <f>J7-I7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>C2/M4</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>C2 (=madre)</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="F8" s="11">
+        <f>1.32^11</f>
+        <v/>
+      </c>
+      <c r="G8" s="11">
+        <f>F8*(1+50.4/100)</f>
+        <v/>
+      </c>
+      <c r="H8" s="6">
+        <f>ROUNDUP((I7+45)/(G8-1)/0.5,0)*0.5</f>
+        <v/>
+      </c>
+      <c r="I8" s="6">
+        <f>I7+H8</f>
+        <v/>
+      </c>
+      <c r="J8" s="6">
+        <f>H8*G8</f>
+        <v/>
+      </c>
+      <c r="K8" s="6">
+        <f>J8-I8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>C2/M5</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>C2 (=madre)</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" s="11">
+        <f>1.32^10</f>
+        <v/>
+      </c>
+      <c r="G9" s="11">
+        <f>F9*(1+41.9/100)</f>
+        <v/>
+      </c>
+      <c r="H9" s="6">
+        <f>ROUNDUP((I8+45)/(G9-1)/0.5,0)*0.5</f>
+        <v/>
+      </c>
+      <c r="I9" s="6">
+        <f>I8+H9</f>
+        <v/>
+      </c>
+      <c r="J9" s="6">
+        <f>H9*G9</f>
+        <v/>
+      </c>
+      <c r="K9" s="6">
+        <f>J9-I9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>C2/M6</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>C2 (=madre)</t>
+        </is>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>9</v>
+      </c>
+      <c r="F10" s="11">
+        <f>1.32^9</f>
+        <v/>
+      </c>
+      <c r="G10" s="11">
+        <f>F10*(1+33.8/100)</f>
+        <v/>
+      </c>
+      <c r="H10" s="6">
+        <f>ROUNDUP((I9+45)/(G10-1)/0.5,0)*0.5</f>
+        <v/>
+      </c>
+      <c r="I10" s="6">
+        <f>I9+H10</f>
+        <v/>
+      </c>
+      <c r="J10" s="6">
+        <f>H10*G10</f>
+        <v/>
+      </c>
+      <c r="K10" s="6">
+        <f>J10-I10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>C2/M7</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>C2 (=madre)</t>
+        </is>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="F11" s="11">
+        <f>1.32^8</f>
+        <v/>
+      </c>
+      <c r="G11" s="11">
+        <f>F11*(1+26.2/100)</f>
+        <v/>
+      </c>
+      <c r="H11" s="6">
+        <f>ROUNDUP((I10+45)/(G11-1)/0.5,0)*0.5</f>
+        <v/>
+      </c>
+      <c r="I11" s="6">
+        <f>I10+H11</f>
+        <v/>
+      </c>
+      <c r="J11" s="6">
+        <f>H11*G11</f>
+        <v/>
+      </c>
+      <c r="K11" s="6">
+        <f>J11-I11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Lock</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Exchange</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>LOCK</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Exchange</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="G12" s="9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="H12" s="8">
+        <f>ROUNDUP((I11+45)/(G12-1)/0.5,0)*0.5</f>
+        <v/>
+      </c>
+      <c r="I12" s="8">
+        <f>I11+H12</f>
+        <v/>
+      </c>
+      <c r="J12" s="8">
+        <f>H12*G12</f>
+        <v/>
+      </c>
+      <c r="K12" s="8">
+        <f>J12-I12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>VERIFICA ROLLOVER</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Perso con S0 (M2 Over)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>I5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Stake C2 piazzata</t>
+        </is>
+      </c>
+      <c r="B16" s="6">
+        <f>H6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Spesa totale se C2 vince subito</t>
+        </is>
+      </c>
+      <c r="B17" s="5">
+        <f>I6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Lordo C2 (copre speso + target?)</t>
+        </is>
+      </c>
+      <c r="B18" s="13">
+        <f>J6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Netto C2 (&gt;=45 = rollover OK)</t>
+        </is>
+      </c>
+      <c r="B19" s="13">
+        <f>K6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Costo totale ciclo (fino a lock)</t>
+        </is>
+      </c>
+      <c r="B20" s="5">
+        <f>I12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Netto Lock</t>
+        </is>
+      </c>
+      <c r="B21" s="6">
+        <f>K12</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>